--- a/public/data/jadwal.xlsx
+++ b/public/data/jadwal.xlsx
@@ -8,26 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Semeru Tour And Travel\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F934522-85EA-47B5-89F4-6A535DD5A891}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379426B7-C075-4D5C-862E-AAA17781C35B}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mei" sheetId="1" r:id="rId1"/>
-    <sheet name="Juni" sheetId="2" r:id="rId2"/>
-    <sheet name="Juli" sheetId="3" r:id="rId3"/>
+    <sheet name="Januari" sheetId="1" r:id="rId1"/>
+    <sheet name="Februari" sheetId="2" r:id="rId2"/>
+    <sheet name="Maret" sheetId="3" r:id="rId3"/>
+    <sheet name="April" sheetId="4" r:id="rId4"/>
+    <sheet name="Mei" sheetId="5" r:id="rId5"/>
+    <sheet name="Juni" sheetId="6" r:id="rId6"/>
+    <sheet name="Juli" sheetId="7" r:id="rId7"/>
+    <sheet name="Agustus" sheetId="8" r:id="rId8"/>
+    <sheet name="September" sheetId="9" r:id="rId9"/>
+    <sheet name="Oktober" sheetId="10" r:id="rId10"/>
+    <sheet name="November" sheetId="11" r:id="rId11"/>
+    <sheet name="Desember" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="16">
   <si>
-    <t>Mei 2026</t>
-  </si>
-  <si>
-    <t/>
+    <t>Januari 2026</t>
   </si>
   <si>
     <t>Tanggal</t>
@@ -36,13 +42,43 @@
     <t>Keterangan</t>
   </si>
   <si>
+    <t>Belum ada order</t>
+  </si>
+  <si>
+    <t>Terbooking</t>
+  </si>
+  <si>
+    <t>Februari 2026</t>
+  </si>
+  <si>
+    <t>Maret 2026</t>
+  </si>
+  <si>
+    <t>April 2026</t>
+  </si>
+  <si>
+    <t>Mei 2026</t>
+  </si>
+  <si>
     <t>Juni 2026</t>
   </si>
   <si>
     <t>Juli 2026</t>
   </si>
   <si>
-    <t>Terbooking</t>
+    <t>Agustus 2026</t>
+  </si>
+  <si>
+    <t>September 2026</t>
+  </si>
+  <si>
+    <t>Oktober 2026</t>
+  </si>
+  <si>
+    <t>November 2026</t>
+  </si>
+  <si>
+    <t>Desember 2026</t>
   </si>
 </sst>
 </file>
@@ -420,554 +456,1352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B3 A5:B10 A4 A12:B19 A11 A23:B30 A20 A21 A22 A31:A34" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B3 A5:B5 A4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3 B4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3 B4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3 B4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>29</v>
-      </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>30</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B5 A20:B28 A6:A19 A29:A33" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -975,280 +1809,1914 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B6 A25:B34 A7:A24" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B3" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3 B4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3 B4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3 B4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3 B4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3 B4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data/jadwal.xlsx
+++ b/public/data/jadwal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Semeru Tour And Travel\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379426B7-C075-4D5C-862E-AAA17781C35B}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397B6BF2-BE55-4C3A-94C6-3F269B2376C5}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2570,7 +2570,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -2623,6 +2623,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A1:B3 B4" numberStoredAsText="1"/>
   </ignoredErrors>
